--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484084_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484084_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2911</v>
+        <v>2.2772</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2504</v>
+        <v>3.1904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0407</v>
+        <v>-0.9132</v>
       </c>
       <c r="G2" t="n">
         <v>4.3926</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5098</v>
+        <v>0.4959</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2472</v>
+        <v>0.1872</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2626</v>
+        <v>0.3087</v>
       </c>
       <c r="V2" t="n">
         <v>-2.4129</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2046</v>
+        <v>2.1828</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6104</v>
+        <v>1.6727</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5942</v>
+        <v>0.51</v>
       </c>
       <c r="G3" t="n">
         <v>0.9684</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0459</v>
+        <v>0.0241</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0171</v>
+        <v>0.0794</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0288</v>
+        <v>-0.0554</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3913</v>
+        <v>1.5276</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0897</v>
+        <v>0.0746</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4811</v>
+        <v>1.453</v>
       </c>
       <c r="G4" t="n">
         <v>0.7015</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3642</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.442</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1058</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7804</v>
+        <v>1.2727</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1647</v>
+        <v>0.5728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6158</v>
+        <v>0.6999</v>
       </c>
       <c r="G5" t="n">
         <v>0.7653</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0605</v>
+        <v>-0.5682</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0599</v>
+        <v>-0.6518</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="V5" t="n">
         <v>1.4724</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1514</v>
+        <v>0.0808</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3004</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3531</v>
+        <v>0.3812</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0454</v>
@@ -922,13 +922,13 @@
         <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3044</v>
+        <v>-0.0723</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.187</v>
+        <v>0.017</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9856</v>
+        <v>-0.3748</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2942</v>
+        <v>0.1762</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6913</v>
+        <v>-0.551</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8859</v>
@@ -1000,13 +1000,13 @@
         <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3575</v>
+        <v>-0.7468</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1619</v>
+        <v>-0.6914</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1957</v>
+        <v>-0.0554</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5219</v>
+        <v>-1.3255</v>
       </c>
       <c r="E8" t="n">
         <v>-1.8254</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3035</v>
+        <v>0.4999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7912</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6513</v>
+        <v>-0.4549</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0679</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5833</v>
+        <v>-0.3869</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>A. FIGUERAS GÜELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8054</v>
+        <v>-1.859</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7104</v>
+        <v>-1.637</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9051</v>
+        <v>-0.222</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9476</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1288</v>
+        <v>-0.7054</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8188</v>
+        <v>-0.2254</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8999</v>
+        <v>-0.5997</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3402</v>
+        <v>-0.6399</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5597</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0477</v>
+        <v>-0.3312</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2114</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2591</v>
+        <v>-0.2656</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3407</v>
+        <v>-0.1346</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1814</v>
+        <v>-0.0453</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1592</v>
+        <v>-0.0893</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FIGUERAS GÜELL</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0911</v>
+        <v>-2.2976</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.841</v>
+        <v>-3.1185</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2501</v>
+        <v>0.8209</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.9476</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7054</v>
+        <v>-1.1288</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2254</v>
+        <v>-0.8188</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5997</v>
+        <v>-1.8999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6399</v>
+        <v>-1.3402</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-0.5597</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3312</v>
+        <v>-0.0477</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.2114</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2656</v>
+        <v>-0.2591</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3667</v>
+        <v>-0.1516</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2494</v>
+        <v>-0.2267</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1173</v>
+        <v>0.0751</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1835</v>
+        <v>-3.2438</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0238</v>
+        <v>-3.7574</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1597</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8826000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9997</v>
+        <v>-1.0599</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9181</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0816</v>
+        <v>-0.4083</v>
       </c>
       <c r="V11" t="n">
         <v>1.2777</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.071499999999999</v>
+        <v>-1.7596</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2635</v>
+        <v>-4.952</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1924</v>
+        <v>3.192299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.3442</v>
@@ -1363,7 +1363,7 @@
         <v>-2.7859</v>
       </c>
       <c r="J12" t="n">
-        <v>7.6339</v>
+        <v>7.633900000000001</v>
       </c>
       <c r="K12" t="n">
         <v>4.5905</v>
@@ -1390,13 +1390,13 @@
         <v>12.895</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3442</v>
+        <v>-3.0325</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.8049</v>
+        <v>-2.4932</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5394000000000001</v>
+        <v>-0.5395000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.07130000000000014</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8906</v>
+        <v>4.2604</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9418</v>
+        <v>2.452</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9487</v>
+        <v>1.8084</v>
       </c>
       <c r="G13" t="n">
         <v>2.6804</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4166</v>
+        <v>0.7865</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2323</v>
+        <v>0.2779</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6489</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8197</v>
+        <v>2.4073</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6605</v>
+        <v>0.294</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1592</v>
+        <v>2.1134</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6169</v>
+        <v>1.6529</v>
       </c>
       <c r="H14" t="n">
-        <v>1.407</v>
+        <v>-0.9124</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2099</v>
+        <v>2.5652</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1567</v>
+        <v>2.2615</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2644</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1077</v>
+        <v>3.0574</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.6086</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3176</v>
+        <v>-0.4921</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9368</v>
+        <v>0.5399</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5589</v>
+        <v>-0.1982</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3779</v>
+        <v>0.7382</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3373</v>
+        <v>1.2065</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8828</v>
+        <v>2.0094</v>
       </c>
       <c r="E15" t="n">
-        <v>0.294</v>
+        <v>0.7422</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5888</v>
+        <v>1.2672</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6529</v>
+        <v>1.6169</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9124</v>
+        <v>1.407</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5652</v>
+        <v>0.2099</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2615</v>
+        <v>2.1567</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7959000000000001</v>
+        <v>2.2644</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0574</v>
+        <v>-0.1077</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6086</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1165</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4921</v>
+        <v>0.3176</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0153</v>
+        <v>1.1266</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1982</v>
+        <v>0.6407</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2136</v>
+        <v>0.4859</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2065</v>
+        <v>-0.3373</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4914</v>
+        <v>1.7252</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7094</v>
+        <v>1.8114</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.218</v>
+        <v>-0.0862</v>
       </c>
       <c r="G16" t="n">
         <v>2.5943</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.615</v>
+        <v>0.8488</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1362</v>
+        <v>0.2382</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4788</v>
+        <v>0.6106</v>
       </c>
       <c r="V16" t="n">
         <v>0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3525</v>
+        <v>0.1984</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.368</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7205</v>
+        <v>0.1984</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2217</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8642</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3575</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.1919</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.6724</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5195</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0298</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1918</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6499</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.442</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.0919</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1984</v>
+        <v>-0.3353</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-2.2659</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1984</v>
+        <v>1.9307</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-2.2217</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.8642</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.3575</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-2.1919</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.6724</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.0298</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.1918</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.9621</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3021</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0414</v>
+        <v>-1.607</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6737</v>
+        <v>-2.5717</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6323</v>
+        <v>0.9647</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1222</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0176</v>
+        <v>0.452</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0171</v>
+        <v>0.1191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0005</v>
+        <v>0.3329</v>
       </c>
       <c r="V19" t="n">
         <v>0.6745</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1191</v>
+        <v>-1.9627</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2672</v>
+        <v>-1.4713</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8519</v>
+        <v>-0.4914</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5716</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1507</v>
+        <v>0.0057</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2438</v>
+        <v>0.0397</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3945</v>
+        <v>-0.034</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4035</v>
+        <v>-3.2642</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4892</v>
+        <v>-2.1831</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9143</v>
+        <v>-1.0811</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9732</v>
@@ -2092,13 +2092,13 @@
         <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1563</v>
+        <v>-0.017</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.544</v>
+        <v>-0.2379</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6122</v>
+        <v>0.2209</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4724</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.0714</v>
+        <v>3.4315</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.192399999999999</v>
+        <v>-3.1924</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2637</v>
+        <v>6.6241</v>
       </c>
       <c r="G22" t="n">
         <v>-1.344200000000001</v>
@@ -2170,13 +2170,13 @@
         <v>12.895</v>
       </c>
       <c r="S22" t="n">
-        <v>3.344200000000001</v>
+        <v>4.7046</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5394999999999999</v>
+        <v>0.5395</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8049</v>
+        <v>4.1652</v>
       </c>
       <c r="V22" t="n">
         <v>0.07129999999999992</v>
